--- a/缓存数据/infoPlow_Monitor_Dept.xlsx
+++ b/缓存数据/infoPlow_Monitor_Dept.xlsx
@@ -733,94 +733,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>123261.89</v>
+        <v>145381.08</v>
       </c>
       <c r="C4" t="n">
         <v>56</v>
       </c>
       <c r="D4" t="n">
-        <v>2201.105178571428</v>
+        <v>2596.090714285714</v>
       </c>
       <c r="E4" t="n">
-        <v>794.88</v>
+        <v>788.5800000000002</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>198.72</v>
+        <v>197.145</v>
       </c>
       <c r="H4" t="n">
-        <v>3899.059999999999</v>
+        <v>4100.76</v>
       </c>
       <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>455.64</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>222.85</v>
+      </c>
+      <c r="O4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="n">
-        <v>487.3824999999999</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>229.58</v>
-      </c>
-      <c r="O4" t="n">
-        <v>9</v>
-      </c>
       <c r="P4" t="n">
-        <v>25.50888888888889</v>
+        <v>27.85625</v>
       </c>
       <c r="Q4" t="n">
-        <v>191.24</v>
+        <v>181.67</v>
       </c>
       <c r="R4" t="n">
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>63.74666666666667</v>
+        <v>60.55666666666667</v>
       </c>
       <c r="T4" t="n">
-        <v>8698.420000000002</v>
+        <v>8602.709999999999</v>
       </c>
       <c r="U4" t="n">
         <v>24</v>
       </c>
       <c r="V4" t="n">
-        <v>362.4341666666667</v>
+        <v>358.44625</v>
       </c>
       <c r="W4" t="n">
-        <v>20173.51</v>
+        <v>20625.66</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>1440.965</v>
+        <v>1289.10375</v>
       </c>
       <c r="Z4" t="n">
-        <v>207.56</v>
+        <v>311.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4" t="n">
-        <v>41.512</v>
+        <v>51.94</v>
       </c>
       <c r="AC4" t="n">
-        <v>325059.7100000003</v>
+        <v>324895.5699999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="AE4" t="n">
-        <v>880.9206233062339</v>
+        <v>864.0839627659573</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -832,13 +832,13 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>157456.1399999997</v>
+        <v>180214.95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AK4" t="n">
-        <v>1280.131219512193</v>
+        <v>1430.277380952381</v>
       </c>
     </row>
     <row r="5">
@@ -848,31 +848,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>145381.08</v>
+        <v>174865.67</v>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D5" t="n">
-        <v>2596.090714285714</v>
+        <v>3179.375818181818</v>
       </c>
       <c r="E5" t="n">
-        <v>788.5800000000002</v>
+        <v>778.3099999999999</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>197.145</v>
+        <v>194.5775</v>
       </c>
       <c r="H5" t="n">
-        <v>4100.76</v>
+        <v>3997.59</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>455.64</v>
+        <v>444.1766666666667</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -884,58 +884,58 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>222.85</v>
+        <v>219.79</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>27.85625</v>
+        <v>27.47375</v>
       </c>
       <c r="Q5" t="n">
-        <v>181.67</v>
+        <v>220.77</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>60.55666666666667</v>
+        <v>55.1925</v>
       </c>
       <c r="T5" t="n">
-        <v>8602.709999999999</v>
+        <v>7756.18</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
       </c>
       <c r="V5" t="n">
-        <v>358.44625</v>
+        <v>323.1741666666667</v>
       </c>
       <c r="W5" t="n">
-        <v>20625.66</v>
+        <v>19969.58</v>
       </c>
       <c r="X5" t="n">
         <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>1289.10375</v>
+        <v>1248.09875</v>
       </c>
       <c r="Z5" t="n">
-        <v>311.64</v>
+        <v>887.92</v>
       </c>
       <c r="AA5" t="n">
         <v>6</v>
       </c>
       <c r="AB5" t="n">
-        <v>51.94</v>
+        <v>147.9866666666667</v>
       </c>
       <c r="AC5" t="n">
-        <v>324895.5699999999</v>
+        <v>361294.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="AE5" t="n">
-        <v>864.0839627659572</v>
+        <v>907.7754271356783</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>180214.9500000001</v>
+        <v>208695.8099999999</v>
       </c>
       <c r="AJ5" t="n">
         <v>126</v>
       </c>
       <c r="AK5" t="n">
-        <v>1430.277380952382</v>
+        <v>1656.315952380952</v>
       </c>
     </row>
     <row r="6">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>174865.67</v>
+        <v>178841.83</v>
       </c>
       <c r="C6" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>3179.375818181818</v>
+        <v>3506.702549019607</v>
       </c>
       <c r="E6" t="n">
-        <v>778.3099999999999</v>
+        <v>817.6600000000001</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>194.5775</v>
+        <v>204.415</v>
       </c>
       <c r="H6" t="n">
-        <v>3997.59</v>
+        <v>3879.98</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>444.1766666666667</v>
+        <v>431.1088888888889</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -999,58 +999,58 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>219.79</v>
+        <v>106.74</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>27.47375</v>
+        <v>26.685</v>
       </c>
       <c r="Q6" t="n">
-        <v>220.77</v>
+        <v>206.24</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>55.1925</v>
+        <v>41.248</v>
       </c>
       <c r="T6" t="n">
-        <v>7756.179999999999</v>
+        <v>8445.170000000004</v>
       </c>
       <c r="U6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V6" t="n">
-        <v>323.1741666666666</v>
+        <v>367.1813043478263</v>
       </c>
       <c r="W6" t="n">
-        <v>19969.58</v>
+        <v>19103.22</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>1248.09875</v>
+        <v>1193.95125</v>
       </c>
       <c r="Z6" t="n">
-        <v>887.92</v>
+        <v>791.6799999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>6</v>
       </c>
       <c r="AB6" t="n">
-        <v>147.9866666666667</v>
+        <v>131.9466666666667</v>
       </c>
       <c r="AC6" t="n">
-        <v>361294.62</v>
+        <v>372461.6499999998</v>
       </c>
       <c r="AD6" t="n">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="AE6" t="n">
-        <v>907.7754271356783</v>
+        <v>975.0304973821985</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>208695.8100000001</v>
+        <v>212192.5200000002</v>
       </c>
       <c r="AJ6" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="AK6" t="n">
-        <v>1656.315952380953</v>
+        <v>1798.241694915256</v>
       </c>
     </row>
     <row r="7">
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>178841.83</v>
+        <v>149009.1899999999</v>
       </c>
       <c r="C7" t="n">
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>3506.702549019607</v>
+        <v>2921.748823529411</v>
       </c>
       <c r="E7" t="n">
-        <v>817.6600000000001</v>
+        <v>788.35</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>204.415</v>
+        <v>197.0875</v>
       </c>
       <c r="H7" t="n">
-        <v>3879.98</v>
+        <v>3829.01</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>431.1088888888889</v>
+        <v>382.901</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1114,58 +1114,58 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>106.74</v>
+        <v>127.13</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>26.685</v>
+        <v>31.7825</v>
       </c>
       <c r="Q7" t="n">
-        <v>206.24</v>
+        <v>214.88</v>
       </c>
       <c r="R7" t="n">
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>41.248</v>
+        <v>42.97600000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>8445.170000000002</v>
+        <v>10326.63</v>
       </c>
       <c r="U7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V7" t="n">
-        <v>367.1813043478261</v>
+        <v>430.2762500000001</v>
       </c>
       <c r="W7" t="n">
-        <v>19103.22</v>
+        <v>19885.78</v>
       </c>
       <c r="X7" t="n">
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>1193.95125</v>
+        <v>1242.86125</v>
       </c>
       <c r="Z7" t="n">
-        <v>791.6800000000001</v>
+        <v>399.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>131.9466666666667</v>
+        <v>79.81800000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>372461.6499999998</v>
+        <v>332628.0399999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AE7" t="n">
-        <v>975.0304973821984</v>
+        <v>877.6465435356197</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1177,13 +1177,13 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>212192.5200000003</v>
+        <v>184580.0600000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK7" t="n">
-        <v>1798.241694915256</v>
+        <v>1551.092941176472</v>
       </c>
     </row>
     <row r="8">
@@ -1193,31 +1193,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>149009.19</v>
+        <v>140255.07</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>2921.748823529411</v>
+        <v>2597.316111111111</v>
       </c>
       <c r="E8" t="n">
-        <v>788.35</v>
+        <v>790</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>197.0875</v>
+        <v>197.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3829.01</v>
+        <v>3767.54</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>382.901</v>
+        <v>418.6155555555555</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1229,58 +1229,58 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>127.13</v>
+        <v>198.64</v>
       </c>
       <c r="O8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>182.52</v>
+      </c>
+      <c r="R8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
-        <v>31.7825</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>214.88</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5</v>
-      </c>
       <c r="S8" t="n">
-        <v>42.97600000000001</v>
+        <v>45.63</v>
       </c>
       <c r="T8" t="n">
-        <v>10326.63</v>
+        <v>9599.85</v>
       </c>
       <c r="U8" t="n">
         <v>24</v>
       </c>
       <c r="V8" t="n">
-        <v>430.2762500000001</v>
+        <v>399.99375</v>
       </c>
       <c r="W8" t="n">
-        <v>19885.78</v>
+        <v>16342.55</v>
       </c>
       <c r="X8" t="n">
         <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>1242.86125</v>
+        <v>1021.409375</v>
       </c>
       <c r="Z8" t="n">
-        <v>399.09</v>
+        <v>718.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB8" t="n">
-        <v>79.818</v>
+        <v>119.825</v>
       </c>
       <c r="AC8" t="n">
-        <v>332628.0399999999</v>
+        <v>311344.2099999999</v>
       </c>
       <c r="AD8" t="n">
         <v>379</v>
       </c>
       <c r="AE8" t="n">
-        <v>877.6465435356198</v>
+        <v>821.488680738786</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>184580.0600000001</v>
+        <v>171855.1200000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AK8" t="n">
-        <v>1551.092941176471</v>
+        <v>1374.84096</v>
       </c>
     </row>
     <row r="9">
@@ -1308,31 +1308,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140255.0699999999</v>
+        <v>146435.3999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>2597.31611111111</v>
+        <v>2662.461818181817</v>
       </c>
       <c r="E9" t="n">
-        <v>790</v>
+        <v>784.2399999999999</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>197.5</v>
+        <v>196.06</v>
       </c>
       <c r="H9" t="n">
-        <v>3767.54</v>
+        <v>3738.17</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>418.6155555555556</v>
+        <v>467.27125</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1344,58 +1344,58 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>198.64</v>
+        <v>206.18</v>
       </c>
       <c r="O9" t="n">
         <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>24.83</v>
+        <v>25.7725</v>
       </c>
       <c r="Q9" t="n">
-        <v>182.52</v>
+        <v>198.09</v>
       </c>
       <c r="R9" t="n">
         <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>45.63</v>
+        <v>49.52250000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>9599.85</v>
+        <v>8183.110000000001</v>
       </c>
       <c r="U9" t="n">
         <v>24</v>
       </c>
       <c r="V9" t="n">
-        <v>399.99375</v>
+        <v>340.9629166666667</v>
       </c>
       <c r="W9" t="n">
-        <v>16342.55</v>
+        <v>15226.17</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>1021.409375</v>
+        <v>951.6356250000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>718.95</v>
+        <v>223.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>119.825</v>
+        <v>44.698</v>
       </c>
       <c r="AC9" t="n">
-        <v>311344.21</v>
+        <v>335440.7800000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="AE9" t="n">
-        <v>821.4886807387862</v>
+        <v>860.1045641025643</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1407,13 +1407,13 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>171855.12</v>
+        <v>174994.8499999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AK9" t="n">
-        <v>1374.84096</v>
+        <v>1411.24879032258</v>
       </c>
     </row>
     <row r="10">
@@ -1423,31 +1423,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>146435.3999999999</v>
+        <v>157678.03</v>
       </c>
       <c r="C10" t="n">
         <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>2662.461818181817</v>
+        <v>2866.873272727273</v>
       </c>
       <c r="E10" t="n">
-        <v>784.2399999999999</v>
+        <v>764.29</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>196.06</v>
+        <v>191.0725</v>
       </c>
       <c r="H10" t="n">
-        <v>3738.17</v>
+        <v>3842.47</v>
       </c>
       <c r="I10" t="n">
         <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>467.27125</v>
+        <v>480.30875</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1459,58 +1459,58 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>206.18</v>
+        <v>523.0099999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>25.7725</v>
+        <v>58.11222222222221</v>
       </c>
       <c r="Q10" t="n">
-        <v>198.09</v>
+        <v>120.69</v>
       </c>
       <c r="R10" t="n">
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>49.52250000000001</v>
+        <v>30.1725</v>
       </c>
       <c r="T10" t="n">
-        <v>8183.110000000001</v>
+        <v>8253.16</v>
       </c>
       <c r="U10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>340.9629166666667</v>
+        <v>358.8330434782609</v>
       </c>
       <c r="W10" t="n">
-        <v>15226.17</v>
+        <v>18883.94</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>951.635625</v>
+        <v>1258.929333333333</v>
       </c>
       <c r="Z10" t="n">
-        <v>223.49</v>
+        <v>236.39</v>
       </c>
       <c r="AA10" t="n">
         <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>44.698</v>
+        <v>47.27800000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>335440.7800000001</v>
+        <v>376177.4500000007</v>
       </c>
       <c r="AD10" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="AE10" t="n">
-        <v>860.1045641025643</v>
+        <v>917.5059756097578</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1522,13 +1522,13 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>174994.8499999999</v>
+        <v>190301.9799999992</v>
       </c>
       <c r="AJ10" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AK10" t="n">
-        <v>1411.24879032258</v>
+        <v>1547.170569105685</v>
       </c>
     </row>
     <row r="11">
@@ -1538,31 +1538,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>157678.0300000001</v>
+        <v>170260.72</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>2866.873272727274</v>
+        <v>3152.976296296296</v>
       </c>
       <c r="E11" t="n">
-        <v>764.29</v>
+        <v>680.0799999999999</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>191.0725</v>
+        <v>170.02</v>
       </c>
       <c r="H11" t="n">
-        <v>3842.47</v>
+        <v>2490.02</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>480.30875</v>
+        <v>311.2525</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1574,58 +1574,58 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>523.01</v>
+        <v>627.1</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>58.11222222222222</v>
+        <v>78.3875</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.69</v>
+        <v>205.93</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>30.1725</v>
+        <v>34.32166666666667</v>
       </c>
       <c r="T11" t="n">
-        <v>8253.16</v>
+        <v>9046.110000000002</v>
       </c>
       <c r="U11" t="n">
         <v>23</v>
       </c>
       <c r="V11" t="n">
-        <v>358.8330434782609</v>
+        <v>393.3091304347827</v>
       </c>
       <c r="W11" t="n">
-        <v>18883.94</v>
+        <v>17261.74</v>
       </c>
       <c r="X11" t="n">
         <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1258.929333333333</v>
+        <v>1150.782666666667</v>
       </c>
       <c r="Z11" t="n">
-        <v>236.39</v>
+        <v>263.87</v>
       </c>
       <c r="AA11" t="n">
         <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>47.278</v>
+        <v>52.774</v>
       </c>
       <c r="AC11" t="n">
-        <v>376177.4500000005</v>
+        <v>407522.0399999998</v>
       </c>
       <c r="AD11" t="n">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="AE11" t="n">
-        <v>917.5059756097572</v>
+        <v>1066.811623036649</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1637,13 +1637,13 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>190301.9799999995</v>
+        <v>200835.5700000002</v>
       </c>
       <c r="AJ11" t="n">
         <v>123</v>
       </c>
       <c r="AK11" t="n">
-        <v>1547.170569105687</v>
+        <v>1632.809512195123</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/infoPlow_Monitor_Dept.xlsx
+++ b/缓存数据/infoPlow_Monitor_Dept.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81,18 +81,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -733,94 +733,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>145381.08</v>
+        <v>211918.77</v>
       </c>
       <c r="C4" t="n">
         <v>56</v>
       </c>
       <c r="D4" t="n">
-        <v>2596.090714285714</v>
+        <v>3784.26375</v>
       </c>
       <c r="E4" t="n">
-        <v>788.5800000000002</v>
+        <v>375.61</v>
       </c>
       <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>125.2033333333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>862.28</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>143.7133333333333</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>163.02</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>548.4400000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7</v>
+      </c>
+      <c r="S4" t="n">
+        <v>78.34857142857143</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4300.98</v>
+      </c>
+      <c r="U4" t="n">
+        <v>22</v>
+      </c>
+      <c r="V4" t="n">
+        <v>195.4990909090909</v>
+      </c>
+      <c r="W4" t="n">
+        <v>18090.08</v>
+      </c>
+      <c r="X4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1206.005333333334</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1795.03</v>
+      </c>
+      <c r="AA4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
-        <v>197.145</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4100.76</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>455.64</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>222.85</v>
-      </c>
-      <c r="O4" t="n">
-        <v>8</v>
-      </c>
-      <c r="P4" t="n">
-        <v>27.85625</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>181.67</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>60.55666666666667</v>
-      </c>
-      <c r="T4" t="n">
-        <v>8602.709999999999</v>
-      </c>
-      <c r="U4" t="n">
-        <v>24</v>
-      </c>
-      <c r="V4" t="n">
-        <v>358.44625</v>
-      </c>
-      <c r="W4" t="n">
-        <v>20625.66</v>
-      </c>
-      <c r="X4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1289.10375</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>311.64</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>6</v>
-      </c>
       <c r="AB4" t="n">
-        <v>51.94</v>
+        <v>448.7575000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>324895.5699999999</v>
+        <v>223773.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="AE4" t="n">
-        <v>864.0839627659573</v>
+        <v>669.9820059880238</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -832,13 +832,13 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>180214.95</v>
+        <v>238054.2100000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AK4" t="n">
-        <v>1430.277380952381</v>
+        <v>2000.455546218488</v>
       </c>
     </row>
     <row r="5">
@@ -848,94 +848,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>174865.67</v>
+        <v>183090.62</v>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>3179.375818181818</v>
+        <v>3269.475357142857</v>
       </c>
       <c r="E5" t="n">
-        <v>778.3099999999999</v>
+        <v>340.86</v>
       </c>
       <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>113.62</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2076.76</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>346.1266666666667</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>759.03</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>108.4328571428571</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1244.59</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>177.7985714285714</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3251.719999999999</v>
+      </c>
+      <c r="U5" t="n">
+        <v>21</v>
+      </c>
+      <c r="V5" t="n">
+        <v>154.8438095238095</v>
+      </c>
+      <c r="W5" t="n">
+        <v>15250.92</v>
+      </c>
+      <c r="X5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1089.351428571428</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2585.52</v>
+      </c>
+      <c r="AA5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>194.5775</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3997.59</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>444.1766666666667</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>219.79</v>
-      </c>
-      <c r="O5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P5" t="n">
-        <v>27.47375</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="R5" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>55.1925</v>
-      </c>
-      <c r="T5" t="n">
-        <v>7756.18</v>
-      </c>
-      <c r="U5" t="n">
-        <v>24</v>
-      </c>
-      <c r="V5" t="n">
-        <v>323.1741666666667</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19969.58</v>
-      </c>
-      <c r="X5" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1248.09875</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>887.92</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6</v>
-      </c>
       <c r="AB5" t="n">
-        <v>147.9866666666667</v>
+        <v>646.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>361294.62</v>
+        <v>216338.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="AE5" t="n">
-        <v>907.7754271356783</v>
+        <v>684.6157911392406</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>208695.8099999999</v>
+        <v>208600.02</v>
       </c>
       <c r="AJ5" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="AK5" t="n">
-        <v>1656.315952380952</v>
+        <v>1767.796779661017</v>
       </c>
     </row>
     <row r="6">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>178841.83</v>
+        <v>155508.58</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D6" t="n">
-        <v>3506.702549019607</v>
+        <v>2728.220701754386</v>
       </c>
       <c r="E6" t="n">
-        <v>817.6600000000001</v>
+        <v>603.3100000000001</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>204.415</v>
+        <v>150.8275</v>
       </c>
       <c r="H6" t="n">
-        <v>3879.98</v>
+        <v>1799.43</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>431.1088888888889</v>
+        <v>257.0614285714286</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -999,58 +999,58 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>106.74</v>
+        <v>160.66</v>
       </c>
       <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>26.77666666666667</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1533.7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4262.070000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>20</v>
+      </c>
+      <c r="V6" t="n">
+        <v>213.1035</v>
+      </c>
+      <c r="W6" t="n">
+        <v>14310.16</v>
+      </c>
+      <c r="X6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1022.154285714286</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2726.35</v>
+      </c>
+      <c r="AA6" t="n">
         <v>4</v>
       </c>
-      <c r="P6" t="n">
-        <v>26.685</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>206.24</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>41.248</v>
-      </c>
-      <c r="T6" t="n">
-        <v>8445.170000000004</v>
-      </c>
-      <c r="U6" t="n">
-        <v>23</v>
-      </c>
-      <c r="V6" t="n">
-        <v>367.1813043478263</v>
-      </c>
-      <c r="W6" t="n">
-        <v>19103.22</v>
-      </c>
-      <c r="X6" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1193.95125</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>791.6799999999999</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6</v>
-      </c>
       <c r="AB6" t="n">
-        <v>131.9466666666667</v>
+        <v>681.5875</v>
       </c>
       <c r="AC6" t="n">
-        <v>372461.6499999998</v>
+        <v>194591.0500000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="AE6" t="n">
-        <v>975.0304973821985</v>
+        <v>627.7130645161293</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>212192.5200000002</v>
+        <v>180904.26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="n">
-        <v>1798.241694915256</v>
+        <v>1520.203865546218</v>
       </c>
     </row>
     <row r="7">
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149009.1899999999</v>
+        <v>200015.83</v>
       </c>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>2921.748823529411</v>
+        <v>3509.049649122806</v>
       </c>
       <c r="E7" t="n">
-        <v>788.35</v>
+        <v>782.7900000000001</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>197.0875</v>
+        <v>195.6975</v>
       </c>
       <c r="H7" t="n">
-        <v>3829.01</v>
+        <v>2756.15</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>382.901</v>
+        <v>459.3583333333333</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1114,58 +1114,58 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>127.13</v>
+        <v>156.8</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>31.7825</v>
+        <v>31.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>214.88</v>
+        <v>986.8399999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>42.97600000000001</v>
+        <v>164.4733333333333</v>
       </c>
       <c r="T7" t="n">
-        <v>10326.63</v>
+        <v>5048.469999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V7" t="n">
-        <v>430.2762500000001</v>
+        <v>252.4235</v>
       </c>
       <c r="W7" t="n">
-        <v>19885.78</v>
+        <v>16776.97</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1242.86125</v>
+        <v>1290.536153846154</v>
       </c>
       <c r="Z7" t="n">
-        <v>399.09</v>
+        <v>148.02</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>79.81800000000001</v>
+        <v>49.34</v>
       </c>
       <c r="AC7" t="n">
-        <v>332628.0399999999</v>
+        <v>213596.4699999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>379</v>
+        <v>294</v>
       </c>
       <c r="AE7" t="n">
-        <v>877.6465435356197</v>
+        <v>726.5186054421765</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1177,13 +1177,13 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>184580.0600000001</v>
+        <v>226671.8700000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="AK7" t="n">
-        <v>1551.092941176472</v>
+        <v>1988.349736842106</v>
       </c>
     </row>
     <row r="8">
@@ -1193,31 +1193,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140255.07</v>
+        <v>248853.94</v>
       </c>
       <c r="C8" t="n">
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>2597.316111111111</v>
+        <v>4608.406296296297</v>
       </c>
       <c r="E8" t="n">
-        <v>790</v>
+        <v>749.2900000000001</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>197.5</v>
+        <v>187.3225</v>
       </c>
       <c r="H8" t="n">
-        <v>3767.54</v>
+        <v>2689.47</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>418.6155555555555</v>
+        <v>537.894</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1229,58 +1229,58 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>198.64</v>
+        <v>147.4</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>24.83</v>
+        <v>36.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>182.52</v>
+        <v>785.3799999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>45.63</v>
+        <v>130.8966666666666</v>
       </c>
       <c r="T8" t="n">
-        <v>9599.85</v>
+        <v>2766.56</v>
       </c>
       <c r="U8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V8" t="n">
-        <v>399.99375</v>
+        <v>138.328</v>
       </c>
       <c r="W8" t="n">
-        <v>16342.55</v>
+        <v>17032.77</v>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
-        <v>1021.409375</v>
+        <v>1216.626428571429</v>
       </c>
       <c r="Z8" t="n">
-        <v>718.95</v>
+        <v>80.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>119.825</v>
+        <v>40.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>311344.2099999999</v>
+        <v>209518.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>379</v>
+        <v>280</v>
       </c>
       <c r="AE8" t="n">
-        <v>821.488680738786</v>
+        <v>748.2817500000001</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>171855.1200000001</v>
+        <v>273105.51</v>
       </c>
       <c r="AJ8" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="AK8" t="n">
-        <v>1374.84096</v>
+        <v>2505.555137614679</v>
       </c>
     </row>
     <row r="9">
@@ -1308,31 +1308,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146435.3999999999</v>
+        <v>193583.72</v>
       </c>
       <c r="C9" t="n">
         <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>2662.461818181817</v>
+        <v>3519.704</v>
       </c>
       <c r="E9" t="n">
-        <v>784.2399999999999</v>
+        <v>747.01</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>196.06</v>
+        <v>186.7525</v>
       </c>
       <c r="H9" t="n">
-        <v>3738.17</v>
+        <v>1456.33</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>467.27125</v>
+        <v>242.7216666666667</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1344,58 +1344,58 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>206.18</v>
+        <v>178.84</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>25.7725</v>
+        <v>25.54857142857143</v>
       </c>
       <c r="Q9" t="n">
-        <v>198.09</v>
+        <v>759.76</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>49.52250000000001</v>
+        <v>108.5371428571429</v>
       </c>
       <c r="T9" t="n">
-        <v>8183.110000000001</v>
+        <v>1763.99</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V9" t="n">
-        <v>340.9629166666667</v>
+        <v>88.1995</v>
       </c>
       <c r="W9" t="n">
-        <v>15226.17</v>
+        <v>17023.47</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>951.6356250000001</v>
+        <v>1309.497692307692</v>
       </c>
       <c r="Z9" t="n">
-        <v>223.49</v>
+        <v>170.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
-        <v>44.698</v>
+        <v>56.81</v>
       </c>
       <c r="AC9" t="n">
-        <v>335440.7800000001</v>
+        <v>193661.6699999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>390</v>
+        <v>279</v>
       </c>
       <c r="AE9" t="n">
-        <v>860.1045641025643</v>
+        <v>694.1278494623654</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1407,13 +1407,13 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>174994.8499999999</v>
+        <v>215683.55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="AK9" t="n">
-        <v>1411.24879032258</v>
+        <v>1875.509130434783</v>
       </c>
     </row>
     <row r="10">
@@ -1423,31 +1423,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157678.03</v>
+        <v>191486.43</v>
       </c>
       <c r="C10" t="n">
         <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>2866.873272727273</v>
+        <v>3481.571454545454</v>
       </c>
       <c r="E10" t="n">
-        <v>764.29</v>
+        <v>746.8099999999999</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>191.0725</v>
+        <v>186.7025</v>
       </c>
       <c r="H10" t="n">
-        <v>3842.47</v>
+        <v>2097.22</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>480.30875</v>
+        <v>349.5366666666666</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1459,58 +1459,58 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>523.0099999999999</v>
+        <v>179.93</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>58.11222222222221</v>
+        <v>25.70428571428571</v>
       </c>
       <c r="Q10" t="n">
-        <v>120.69</v>
+        <v>804.4400000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1725</v>
+        <v>114.92</v>
       </c>
       <c r="T10" t="n">
-        <v>8253.16</v>
+        <v>3105.760000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="V10" t="n">
-        <v>358.8330434782609</v>
+        <v>155.2880000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>18883.94</v>
+        <v>17612.77</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1258.929333333333</v>
+        <v>1258.055</v>
       </c>
       <c r="Z10" t="n">
-        <v>236.39</v>
+        <v>196.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
-        <v>47.27800000000001</v>
+        <v>65.59333333333333</v>
       </c>
       <c r="AC10" t="n">
-        <v>376177.4500000007</v>
+        <v>175431.2800000002</v>
       </c>
       <c r="AD10" t="n">
-        <v>410</v>
+        <v>272</v>
       </c>
       <c r="AE10" t="n">
-        <v>917.5059756097578</v>
+        <v>644.9679411764712</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1522,13 +1522,13 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>190301.9799999992</v>
+        <v>216230.1399999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="AK10" t="n">
-        <v>1547.170569105685</v>
+        <v>1864.052931034482</v>
       </c>
     </row>
     <row r="11">
@@ -1538,31 +1538,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>170260.72</v>
+        <v>164635.36</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>3152.976296296296</v>
+        <v>3292.7072</v>
       </c>
       <c r="E11" t="n">
-        <v>680.0799999999999</v>
+        <v>746.78</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>170.02</v>
+        <v>186.695</v>
       </c>
       <c r="H11" t="n">
-        <v>2490.02</v>
+        <v>3136.11</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>311.2525</v>
+        <v>627.222</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1574,58 +1574,58 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>627.1</v>
+        <v>210.71</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>78.3875</v>
+        <v>35.11833333333333</v>
       </c>
       <c r="Q11" t="n">
-        <v>205.93</v>
+        <v>1433</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>34.32166666666667</v>
+        <v>204.7142857142857</v>
       </c>
       <c r="T11" t="n">
-        <v>9046.110000000002</v>
+        <v>4381.35</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="V11" t="n">
-        <v>393.3091304347827</v>
+        <v>219.0675</v>
       </c>
       <c r="W11" t="n">
-        <v>17261.74</v>
+        <v>14439.45</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1150.782666666667</v>
+        <v>1031.389285714286</v>
       </c>
       <c r="Z11" t="n">
-        <v>263.87</v>
+        <v>202.66</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>52.774</v>
+        <v>67.55333333333333</v>
       </c>
       <c r="AC11" t="n">
-        <v>407522.0399999998</v>
+        <v>167602.8299999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>382</v>
+        <v>244</v>
       </c>
       <c r="AE11" t="n">
-        <v>1066.811623036649</v>
+        <v>686.8968442622947</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1637,13 +1637,13 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>200835.5700000002</v>
+        <v>189185.4200000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AK11" t="n">
-        <v>1632.809512195123</v>
+        <v>1735.646055045872</v>
       </c>
     </row>
   </sheetData>
@@ -1661,6 +1661,6 @@
     <mergeCell ref="AF1:AH1"/>
     <mergeCell ref="Q1:S1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>